--- a/output/c4ai_resumo_grupos.xlsx
+++ b/output/c4ai_resumo_grupos.xlsx
@@ -448,7 +448,7 @@
         <v>144</v>
       </c>
       <c r="C2" t="n">
-        <v>34.86682808716706</v>
+        <v>35.46798029556651</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -457,14 +457,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AGRIBIO</t>
+          <t>KEML</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C3" t="n">
-        <v>14.04358353510896</v>
+        <v>13.79310344827586</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -473,14 +473,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KEML</t>
+          <t>AGRIBIO</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C4" t="n">
-        <v>13.5593220338983</v>
+        <v>13.30049261083744</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -496,7 +496,7 @@
         <v>53</v>
       </c>
       <c r="C5" t="n">
-        <v>12.83292978208232</v>
+        <v>13.05418719211823</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>12.83292978208232</v>
+        <v>12.31527093596059</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -528,7 +528,7 @@
         <v>21</v>
       </c>
       <c r="C7" t="n">
-        <v>5.084745762711865</v>
+        <v>5.172413793103448</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
@@ -544,7 +544,7 @@
         <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>3.631961259079903</v>
+        <v>3.694581280788177</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
@@ -560,7 +560,7 @@
         <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>3.14769975786925</v>
+        <v>3.201970443349754</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>

--- a/output/c4ai_resumo_grupos.xlsx
+++ b/output/c4ai_resumo_grupos.xlsx
@@ -448,7 +448,7 @@
         <v>144</v>
       </c>
       <c r="C2" t="n">
-        <v>35.46798029556651</v>
+        <v>35.38083538083538</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -464,7 +464,7 @@
         <v>56</v>
       </c>
       <c r="C3" t="n">
-        <v>13.79310344827586</v>
+        <v>13.75921375921376</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -477,10 +477,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C4" t="n">
-        <v>13.30049261083744</v>
+        <v>13.51351351351351</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -496,7 +496,7 @@
         <v>53</v>
       </c>
       <c r="C5" t="n">
-        <v>13.05418719211823</v>
+        <v>13.02211302211302</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -512,7 +512,7 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>12.31527093596059</v>
+        <v>12.28501228501229</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -528,7 +528,7 @@
         <v>21</v>
       </c>
       <c r="C7" t="n">
-        <v>5.172413793103448</v>
+        <v>5.159705159705159</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
@@ -544,7 +544,7 @@
         <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>3.694581280788177</v>
+        <v>3.685503685503686</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
@@ -560,7 +560,7 @@
         <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>3.201970443349754</v>
+        <v>3.194103194103194</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
